--- a/EPIC_0005_Ride_Safety_Calls.xlsx
+++ b/EPIC_0005_Ride_Safety_Calls.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Framework_For_WE1_Automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{372B66B2-0197-40A5-94BD-8AADFE3B486B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66346BB1-D980-40E5-BC74-7E1A9DFEFE07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UserDriverWebIntialilzer" sheetId="43" r:id="rId1"/>
     <sheet name="CustomerAppEmergencyNumber" sheetId="48" r:id="rId2"/>
+    <sheet name="PanicCallCheck" sheetId="49" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="36">
   <si>
     <t>Requirement Title</t>
   </si>
@@ -411,6 +412,280 @@
   </si>
   <si>
     <t>TC_RG_01_Emergency_Calls</t>
+  </si>
+  <si>
+    <t>Panic Call Check</t>
+  </si>
+  <si>
+    <t>TC_RG_02_Panic_Call</t>
+  </si>
+  <si>
+    <t>1. Reload the User App completely.
+2. Reload the Driver App completely.
+3. Switch to the Super Admin Web Portal session.
+4. Click on "Dashboard" from the navigation menu.
+5. Click on "Settings" in the navigation menu.
+6. Click on "Panic Call Setting" from the sidebar menu.
+7. Click the "Add Panic Call" button.
+8. Enter the name (Police) into the name input field.
+9. Enter the name in Tamil (காவல்துறை) into the Tamil name input field.
+10. Enter the name in Hindi (पुलिस) into the Hindi name input field.
+11. Enter the contact number (100) into the contact number field.
+12. Click the Status dropdown.
+13. Select "Active" from the status dropdown options.
+14. Click the "Submit" button to save the panic call setting.
+15. Search for the created panic call entry using the name.
+16. Wait 1 second for the search results to load.
+17. Switch to the Driver App session.
+18. Wait for the notification permission dialog to appear.
+19. Tap "Allow" to grant notification permissions.
+20. Set the mock location of the Driver device to Perambur (Coordinates: 13.121030, 80.232578).
+21. Tap "Agree" on the terms and conditions screen.
+22. Tap "Get Started" on the onboarding screen.
+23. Tap "Next" to navigate through onboarding.
+24. Tap the Mobile Number input field.
+25. Tap "Close" to dismiss any system auto-fill popups.
+26. Enter the approved driver mobile number.
+27. Wait for the "Continue" button to become visible.
+28. Tap "Continue".
+29. Enter the verification OTP (123456).
+30. Tap "Allow" to grant location permissions.
+31. Wait for the Driver App home header label to display.
+32. Wait 3 seconds for the Driver App status toggle to turn ON.
+33. Wait an additional 2 seconds to ensure driver online status is active.
+34. Switch back to the User App session.
+35. Wait for the "Get Started" button to display on the User App screen.
+36. Tap "Get Started".
+37. Tap "Allow" to grant notification permissions.
+38. Set the mock location of the User device to Perambur (Coordinates: 13.121030, 80.232578).
+39. Tap "Next".
+40. Tap the Mobile Number input field.
+41. Tap "Close" to dismiss any system auto-fill popups.
+42. Enter the customer mobile number.
+43. Wait for the "Continue" button to become visible.
+44. Tap "Continue".
+45. Enter the verification OTP (123456).
+46. Wait for the "Finish" button to become visible.
+47. Tap "Finish".
+48. Tap "Allow" to grant location permissions.
+49. Wait for the "Auto Ride" option to display on the home screen.
+50. Tap "Auto Ride".
+51. Enter the destination address ("Parsn Manare") into the destination search field.
+52. Wait for the location map selection screen to load.
+53. Tap the first destination suggestion from the search results.
+54. Wait for the entrance location selector to display.
+55. Tap the entrance location option.
+56. Tap "Confirm" to set the destination.
+57. Wait 5 seconds for ride estimation and vehicle availability.
+58. Wait for the "Ride Now" button to become visible.
+59. Tap "Ride Now" to request a booking.
+60. Switch to the Driver App session.
+61. Wait for the ride request notification and Accept button to display.
+62. Tap "Accept Ride" to confirm the booking.
+63. Switch to the User App session.
+64. Wait for the ride OTP display element to load on screen.
+65. Note down/Extract the displayed ride OTP from the screen.
+66. Wait 2 seconds for the ride interface to stabilize.
+67. Tap the "SOS" button on the active ride screen.
+68. Tap the "Police" button from the emergency options.
+69. Tap the "Call" button to initiate the emergency panic call.
+70. Wait 6 seconds for the emergency call action to process and return.
+71. Switch to the User App session.
+72. Switch to the Driver App session.
+73. Wait for the "On My Way" status button to display.
+74. Wait for the "Arrived" status button to display.
+75. Ensure the "Arrived" status button is fully visible.
+76. Tap "Arrived" to update driver arrival status.
+77. Wait for the confirmation dialog button ("Yes") to appear.
+78. Tap "Yes" to confirm arrival.
+79. Wait for the "Start Ride" button to display.
+80. Tap "Start Ride".
+81. Wait for the OTP input field to display.
+82. Enter the extracted ride OTP into the OTP input field.
+83. Wait for the "Start" button to become visible.
+84. Tap the "Start" button to commence the trip.
+85. Wait 3 seconds for the trip to register as started.
+86. Tap the "SOS" button using coordinates (972, 1207).
+87. Tap the "Police / 108 Call" option.
+88. Tap the "Call" button to initiate the panic call from the driver app.
+89. Wait 5 seconds for the phone dialer interface to interact/return.
+90. Switch to the Driver App session.
+91. Wait for the "Complete Ride" button to display.
+92. Tap "Complete Ride".
+93. Wait for the "Collect Payment" button to display.
+94. Tap "Collect Payment".
+95. Switch to the User App session.
+96. Wait for the "Proceed to Pay" button to display.
+97. Tap "Proceed to Pay".
+98. Wait for the payment confirmation option to display.
+99. Tap "Pay Cash" to choose cash as the payment method.
+100. Wait for the "Give Review" screen/button to display.
+101. Tap "Give Review".
+102. Tap the rating stars at coordinates (348, 1619) to set rating.
+103. Tap "Submit Rating".
+104. Wait for the "Done" button to appear.
+105. Tap "Done" to finish the ride process on the customer app.
+106. Switch to the Driver App session.
+107. Wait for the payment "Proceed" button to display.
+108. Tap "Proceed".
+109. Wait for the "Yes" confirmation button to appear.
+110. Tap "Yes" to confirm receipt of payment.
+111. Wait for the "Give Review" button to display.
+112. Tap "Give Review".
+113. Wait 2 seconds for the rating screen to load.
+114. Tap the rating stars at coordinates (348, 1545) to set rating.
+115. Tap "Submit Rating".
+116. Wait for the "Complete" button to display.
+117. Tap "Complete".
+118. Wait for the final ride complete submit button to display.
+119. Tap "Ride Complete Submit".
+120. Switch to the Super Admin Web Portal session.
+121. Click on "Dashboard" from the navigation menu.
+122. Click on "Settings" in the navigation menu.
+123. Click on "Panic Call Setting" from the sidebar menu.
+124. Search for the created panic call entry using the name.
+125. Wait 1 second for search results to load.
+126. Click the "Delete" button for the panic call entry.
+127. Click "Confirm Delete" on the confirmation modal.
+128. Wait 2 seconds for deletion process to complete.</t>
+  </si>
+  <si>
+    <t>This test case validates the end-to-end integration and execution of the Panic Call (SOS) feature across the Super Admin Web Portal, User App, and Driver App during an active Auto Ride session. It covers creating and activating a multilingual emergency contact (Police - 100) in the Admin Portal, configuring driver and customer locations in Perambur, requesting and accepting an Auto Ride, and extracting the OTP to start the trip. It verifies that both customer and driver can successfully trigger the SOS button and initiate emergency police calls during the ride, and completes the flow by processing cash payment, exchanging mutual user-driver reviews, and cleaning up the test data by deleting the panic contact in the Super Admin Portal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin Web portal is accessible and Cutomer and Driver App is availbale in emulator </t>
+  </si>
+  <si>
+    <t>1. Reload User App Completely,reload_app,user,
+2. Reload Driver App Completely,reload_app,driver,
+3. Switch To Web,switch_to,web,
+4. Click Dashboard,Click,,"web.global.menu.dashboard"
+5. Click Setting,click,,"admin.setting.sidebar.menu"
+6. Click Panic call setting,click,,"admin.setting.panic_call.sidebar_menu"
+7. Click Add panic call button,click,,"admin.setting.panic_call.add_btn"
+8. Enter name,type,Police&gt;&gt;policeName,"admin.setting.panic_call.name_input"
+9. Enter name in tamil,type,காவல்துறை,"admin.setting.panic_call.tamil_name_input"
+10. Enter name in hindi,type,पुलिस,"admin.setting.panic_call.hindi_name_input"
+11. Contact number,type,100,"admin.setting.panic_call.contact_number"
+12. Select Status button,click,,"admin.setting.panic_call.status_dropdown"
+13. Select Active status,click,,"admin.setting.panic_call.activate_status_dropdown"
+14. Submit button,click,,"web.global.action.submit"
+15. Search name,type,{policeName},"admin.setting.panic_call.search_name"
+16. Wait For Load,wait,1000,
+17. Load Driver App,switch_to,driver,
+18. Wait For Notification,wait_until_visible,,"mobile.driver.permission_allow.btn"
+19. Click Allow Notification,tap,,"mobile.driver.permission_allow.btn"
+20. Force Driver Location To Perambur,set_location,13.121030;80.232578,
+21. Click Agree,tap,,"mobile.driver.agree.btn"
+22. Click Get Started,tap,,"mobile.driver.get_started.btn"
+23. Click Next,tap,,"mobile.driver.next.btn"
+24. Click Mobile Number,tap,,"mobile.driver.mobile_number_field.btn"
+25. Click Close,tap,,"mobile.driver.cancel.btn"
+26. Enter Mobile Number,type,regression.approved_driver.phone,"mobile.driver.edit_text.input"
+27. Wait for Continue,wait_until_visible,,"mobile.driver.continue.btn"
+28. Click Continue,tap,,"mobile.driver.continue.btn"
+29. Enter OTP,type,123456,"mobile.driver.edit_text.input"
+30. Click Allow Location,tap,,"mobile.driver.location_allow.btn"
+31. Wait For Driver App,wait_until_visible,,"mobile.driver.app_header.label"
+32. Wait For Driver App Toggle On,wait,3000,
+33. Wait For Driver App Toggle On,wait,2000, 
+34. Load User App,switch_to,user,
+35. Wait For Get Started,wait_until_visible,,"mobile.customer.get_started.btn"
+36. Click Get Started,tap,,"mobile.customer.get_started.btn"
+37. Click Allow Notification,tap,,"mobile.customer.permission_allow.btn"
+38. Force User Location To Perambur,set_location,13.121030;80.232578,
+39. Click Next,tap,,"mobile.customer.next.btn"
+40. Click Mobile Number,tap,,"mobile.customer.mobile_number_field.btn"
+41. Click Close,tap,,"mobile.customer.cancel.btn"
+42. Enter Mobile Number,type,regression.customer.phone,"mobile.customer.edit_text.input"
+43. Wait for Continue,wait_until_visible,,"mobile.customer.continue.btn"
+44. Click Continue,tap,,"mobile.customer.continue.btn"
+45. Enter OTP,type,123456,"mobile.customer.otp_input"
+46. Wait for Finish,wait_until_visible,,"mobile.customer.finish.btn"
+47. Click Finish,tap,,"mobile.customer.finish.btn"
+48. Click Allow Location,tap,,"mobile.customer.location_allow.btn"
+49. Wait For Auto Ride,wait_until_visible,,"mobile.customer.auto_ride.btn"
+50. Click Auto Ride,tap,,"mobile.customer.auto_ride.btn"
+51. Enter Destination,type,Parsn Manare,"mobile.customer.destination.input"
+52. Wait for Location,wait_until_visible,,"mobile.customer.set_location_map.btn"
+53. Select Destination,tap,,"mobile.customer.destination_suggestion_first"
+54. Wait For Entrance,wait_until_visible,,"mobile.customer.destination_entrance_location"
+55. Click Entrance,tap,,"mobile.customer.destination_entrance_location"
+56. Click Confirm,tap,,"mobile.customer.confirm.btn"
+57. Wait For Ride,wait,5000,
+58. Wait for Ride,wait_until_visible,,"mobile.customer.ride_now.btn"
+59. Ride Now,tap,,"mobile.customer.ride_now.btn"
+60. Load Driver App,switch_to,driver,
+61. Wait for Accept,wait_until_visible,,"mobie.driver.auto_ride_accept.button"
+62. Click  Accept Ride,tap,,"mobie.driver.auto_ride_accept.button"
+63. Load User App,switch_to,user,
+64. Wait for OTP Layout to Load,wait_until_visible,,"mobile.customer.otp_display_element"
+65. Extract OTP from Screen,store_text,ride_otp,"mobile.customer.otp_display_element"
+66. Wait for load,wait,2000,
+67. Click SOS button,tap,,"mobile.customer.ride.sos_btn"
+68.Wait For Popup,wait,3000,
+69. Click Police bttuon,tap,,"mobile.customer.ride.sos_btn.police_btn"
+70. Click Call Button,tap,,"mobile.customer.ride.sos_btn.police.call_btn"
+71. Wait for reload the screen,wait,6000,
+72. Load Customer Apps,switch_to,user
+73. Load Driver App,switch_to,driver,
+74. Wait for On My Way,wait_until_visible,,"mobile.driver.on_my_way.btn"
+75. Wait for Arrived,wait_until_visible,,"mobile.driver.arrived.btn"
+76. Wait for Arrived,wait_until_visible,,"mobile.driver.arrived.btn"
+77. Ride Arrived,tap,,"mobile.driver.arrived.btn"
+78. Wait for Yes,wait_until_visible,,"mobile.driver.yes.btn"
+79. Yes Arrived,tap,,"mobile.driver.yes.btn"
+80. Wait for Start Ride,wait_until_visible,,"mobile.driver.start_ride.btn"
+81. Start Ride,tap,,"mobile.driver.start_ride.btn"
+82. wait for Otp,wait_until_visible,,"mobile.driver.otp_view.input"
+83. Enter  Extracted OTP,type,{ride_otp},"mobile.driver.otp_view.input"
+84. Wait for Start Button,wait_until_visible,,"mobile.driver.start.btn"
+85. Start Ride Button,tap,,"mobile.driver.start.btn"
+86. wait for data,wait,3000,
+87. Click SOS Button,tap_coordinate ,972:1207,COORDINATE_MODE
+88.Wait For Popup,wait,3000,
+89. Click Police Button,tap,,"mobile.driver.ride.sos.call_108"
+90. Click Call Button,tap,,"mobile.driver.ride.sos.call_btn"
+91. Wait for Phone Dialer,wait,5000,
+92. Load User App,switch_to,driver,
+93. Wait for Complete Ride,wait_until_visible,,"mobile.driver.complete_ride.btn"
+94. Complete Ride,tap,,"mobile.driver.complete_ride.btn"
+95. Wait for Collect Payment,wait_until_visible,,"mobile.driver.collect_payment.btn"
+96. Collect Payment,tap,,"mobile.driver.collect_payment.btn"
+97. Load User App,switch_to,user,
+98. Wait for Proceed Payment,wait_until_visible,,"mobile.customer.proceed_to_pay.btn"
+99. Proceed Payment,tap,,"mobile.customer.proceed_to_pay.btn"
+100. Wait for Proceed Pay Confirm,wait_until_visible,,"mobile.customer.proceed_to_pay.btn"
+101. Pay Cash,tap,,"mobile.customer.proceed_to_pay.btn"
+102. Wait for Review,wait_until_visible,,"mobile.customer.give_review.btn"
+103. Give Review,tap,,"mobile.customer.give_review.btn"
+104. Give Rating,tap_coordinate,348:1619,
+105. Submit Rating,tap,,"mobile.customer.submit_rating.btn"
+106. Wait for Done,wait_until_visible,,"mobile.customer.done.btn"
+107. Trip Finished,tap,,"mobile.customer.done.btn"
+108. Load Driver App,switch_to,driver,
+109. Wait  For Proceed,wait_until_visible,,"mobile.driver.payment.proceed_btn"
+110. Click For Proceed,tap,,"mobile.driver.payment.proceed_btn"
+111. Wait for Yes,wait_until_visible,,"mobile.driver.yes.btn"
+112. Confirm Payment,tap,,"mobile.driver.yes.btn"
+113. Wait For Give Review Button,wait_until_visible,,"mobile.driver.give_review.btn"
+114. Click Give Review Button,tap,,"mobile.driver.give_review.btn"
+115. Wait For Rating,wait,2000,
+116. Give Rating,tap_coordinate,348:1545,
+117. Submit Rating,tap,,"mobile.driver.submit_rating.btn"
+118. Wait for Complete Button,wait_until_visible,,"mobile.driver.complete.btn"
+119. Click Complete Button,tap,,"mobile.driver.complete.btn"
+120. Wait For  ride complete submit button,wait_until_visible,,"mobile.driver.ride_complete_submit.btn"
+121. Click Ride Complete Submit Button,tap,,"mobile.driver.ride_complete_submit.btn"
+122. Switch To Web,switch_to,web,
+123. Click Dashboard,Click,,"web.global.menu.dashboard"
+124. Click Setting,click,,"admin.setting.sidebar.menu"
+125. Click Panic call setting,click,,"admin.setting.panic_call.sidebar_menu"
+126. Search name,type,{policeName},"admin.setting.panic_call.search_name"
+127.Wait For Load,wait,1000,
+128. Delete Panic Call Delete,click,,"admin.setting.panic_call.delete_btn"
+129. Confirm Delete,click,,"admin.setting.panic_call.confirm_delete_btn"
+130. Wait For Delete,wait,2000,</t>
   </si>
 </sst>
 </file>
@@ -948,4 +1223,102 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68BF2064-1F4D-4DE7-9489-136A9D518A49}">
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.33203125" customWidth="1"/>
+    <col min="2" max="2" width="21.5546875" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" customWidth="1"/>
+    <col min="4" max="4" width="28.77734375" customWidth="1"/>
+    <col min="5" max="5" width="29.109375" customWidth="1"/>
+    <col min="6" max="6" width="45.77734375" customWidth="1"/>
+    <col min="7" max="7" width="71.44140625" customWidth="1"/>
+    <col min="8" max="8" width="40.44140625" customWidth="1"/>
+    <col min="9" max="9" width="61.88671875" customWidth="1"/>
+    <col min="10" max="10" width="32.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="1" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/EPIC_0005_Ride_Safety_Calls.xlsx
+++ b/EPIC_0005_Ride_Safety_Calls.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Framework_For_WE1_Automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66346BB1-D980-40E5-BC74-7E1A9DFEFE07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DA09093-C24C-41B6-9D53-2F8A5FA003D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="37">
   <si>
     <t>Requirement Title</t>
   </si>
@@ -686,6 +686,200 @@
 128. Delete Panic Call Delete,click,,"admin.setting.panic_call.delete_btn"
 129. Confirm Delete,click,,"admin.setting.panic_call.confirm_delete_btn"
 130. Wait For Delete,wait,2000,</t>
+  </si>
+  <si>
+    <t>1. Reload User App Completely,reload_app,user,
+2. Reload Driver App Completely,reload_app,driver,
+3.  Switch To Web Session,switch_to,web,
+4. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+5. Click drivers menu,click,,"admin.drivers.menu.icon"
+6. Click Add Driver menu,click,,"admin.drivers.add_menu.link"
+7. Verify Add Driver,verify,,"admin.drivers.add_page.header"
+8. Click Service Category Dropdown,click,,"admin.drivers.service_dropdown.select"
+9. Select Auto Ride Option,click,,"admin.drivers.service_dropdown.auto_ride"
+10.Click Driver Type Dropdown,click,,"admin.drivers.driver_type.dropdown"
+11.Select pilot Option,click,,"admin.drivers.driver_type.dropdown_pilot"
+12. Enter Driver Name, type, autodriver{randomAlpha} &gt;&gt; autoName, "admin.drivers.fullname.input"
+13. Enter Email, type, autodriver_{timestamp}@gmail.com&gt;&gt;autoEmail, "admin.drivers.email.input"
+14. Enter Contact Number, type, {randomPhone}&gt;&gt;autoPhone, "admin.drivers.phone.input"
+15. Click Whatspp, click, , "admin.drivers.whatsapp.checkbox"
+16. Enter Whatspp Number, type, {autoPhone}, "admin.drivers.whatsapp_phone.input"
+17. Upload Profile Image, uploadfile, "src/main/resources/test-data/autodriver.jpg", "admin.drivers.profile_image.file"
+18. Select Source,click,,"admin.drivers.source_dropdown.select"
+19. Select Instagram,click,,"admin.drivers.instagram_option.span"
+20. Select Male Gender, click, , "admin.drivers.male_gender.div"
+21. Click Vehicle Type Dropdown,click,,"admin.drivers.vehicle_dropdown.select"
+22. Select  Auto Option,click,,"admin.drivers.vehicle_option.pinkauto"
+23. Enter Model Year, type, 2013, "admin.drivers.modelyear.input"
+24. Enter Plate No, type, KL-01-AB-1234, "admin.drivers.plateno.input"
+25. Enter Model Name, type, petrol, "admin.drivers.modelname.input"
+26. Upload Vehicle Image, uploadfile, "src/main/resources/test-data/vehicle.jpg", "admin.drivers.vehicle_image.file"
+27. Enter Bank Name, type, HDFC Bank, "admin.drivers.bankname.input"
+28. Enter Bank Location, type, PARK STREET, "admin.drivers.banklocation.input"
+29. Enter Account Number, type, 50100123456789, "admin.drivers.accountno.input"
+30. Enter Account Holder Name, type,{autoName}, "admin.drivers.accountholder.input"
+31. Enter Payment Email Address, type, {autoEmail}, "admin.drivers.paymentemail.input"
+32. Enter IFSC Code, type, HDFC0001234, "admin.drivers.ifsc.input"
+33. Click Submit, click, , "web.global.action.submit"
+34. Verify Driver Added, verify,, "web.global.toast.success"
+35. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+36. Click drivers menu,click,,"admin.drivers.menu.icon"
+37. Click Pending Documents,click,,"admin.drivers.pending_docs.link"
+38. Filter by Name,type,{autoName},"admin.drivers.name_filter.input"
+39. Scroll Grid, tab, 7, "admin.drivers.name_filter.input"
+40. Click Doc Icon,click,,"admin.drivers.docs.icon"
+41. Driver Required Documents,verify,,"admin.drivers.required_docs.header"
+42. FilterDocumet List,type,Driving Licence,"admin.drivers.docs_filter.input"
+43. Add Driving License,click,,"admin.drivers.docs.edit_icon"
+44. Upload Driving Iicense, uploadfile, "src/main/resources/test-data/license.jpg", "admin.drivers.profile_image.file"
+45. Enter Expiry Date,set_date,2026-12-12,"admin.drivers.doc_expiry.input"
+46. Click Submit, click, , "web.global.action.submit"
+47. Verify Updated Succesfully, verify, , "web.global.toast.updated"
+48. Click Approve Driver,click,,"admin.drivers.docs.approval"
+49. Verify Updated Succesfully, verify, , "web.global.toast.updated"
+50. Click Dashboard,click,,"web.global.menu.dashboard"
+51. Click drivers menu,click,,"admin.drivers.menu.icon"
+52. Click Approved Drivers,click,,"admin.drivers.approved_docs.link"
+53. Approved Drivers List,verify,,"admin.drivers.approved_page.header"
+54. Filter Approved Driver,type,{autoName},"admin.drivers.name_filter.input"
+55.Wait For Load,wait,2000,
+56.Scroll Grid,tab,10,"admin.drivers.name_filter.input"
+57.Click Wallet,click,,"admin.drivers.wallet.btn"
+58.Click Manage Transaction,click,,"admin.drivers.wallet.manage_transaction.btn"
+59.Enter Wallet Amout,type,500,"admin.drivers.wallet.wallet_amount_input"
+60.Click Dropdown,click,,"admin.drivers.wallet.option_dropdown"
+61.Select Add Money Optin,click,,"admin.drivers.wallet.option_add_money"
+62.Click Submit Button,click,,"admin.drivers.wallet.submit.btn"
+63.Wait For Recharge,wait,2000,
+64. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+65.Click Customer Icon,click,,"admin.menu.customer_icon"
+66.Click Add Customers,click,,"admin.menu.add_customers"
+67.Wait For Customer Heading,wait_until_visible,,"admin.customer.add_heading"
+68.Enter Customer Name,type,customer{randomAlpha} &gt;&gt; customerName,"admin.customer.input_name"
+69.Enter Email,type,customer_{timestamp}@gmail.com&gt;&gt;customerEmail,"admin.customer.input_email"
+70.Enter Contact Number,type,{randomPhone}&gt;&gt;customerPhone,"admin.customer.input_phone"
+71.Enter Emergency Number,type,{randomPhone},"admin.customer.input_Emergency_phone"
+72.Open Gender,click,,"admin.customer.dropdown_gender"
+73.Select Male,click,,"admin.customer.select_gender_male"
+74.Upload Profile Image,uploadfile,"src/main/resources/test-data/customer.jpg","admin.customer.upload_profile_img"
+75.Click Submit,click,,"web.global.action.submit"
+76.Wait For Added Successfully,wait_until_visible,,"web.global.toast.info"
+77.Click Dashboard,click,,"web.global.menu.dashboard"
+78.Click Customer Icon,click,,"admin.menu.customer_icon"
+79.Click Verified Customers,click,,"admin.menu.verified_customers"
+80.Wait For Customer List Heading,wait_until_visible,,"admin.customer.verified_list_heading"
+81.Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
+82.Wait For Load,wait,2000,
+83. Click Dashboard,Click,,"web.global.menu.dashboard"
+84.Click Setting,click,,"admin.setting.sidebar.menu"
+85.Click Panic call setting,click,,"admin.setting.panic_call.sidebar_menu"
+86.Click Add panic call button,click,,"admin.setting.panic_call.add_btn"
+87.Enter name,type,Police{randomAlpha}&gt;&gt;policeName,"admin.setting.panic_call.name_input"
+88.Enter name in tamil,type,காவல்துறை,"admin.setting.panic_call.tamil_name_input"
+89.Enter name in hindi,type,पुलिस,"admin.setting.panic_call.hindi_name_input"
+90.Contact number,type,100,"admin.setting.panic_call.contact_number"
+91.Select Status button,click,,"admin.setting.panic_call.status_dropdown"
+92.Select Active status,click,,"admin.setting.panic_call.activate_status_dropdown"
+93.Submit button,click,,"web.global.action.submit"
+94.Search name,type,{policeName},"admin.setting.panic_call.search_name"
+95.Wait For Load,wait,1000,
+96. Load Driver App,switch_to,driver,
+97. Wait For Notification,wait_until_visible,,"mobile.driver.permission_allow.btn"
+98. Click Allow Notification,tap,,"mobile.driver.permission_allow.btn"
+99. Click Agree,tap,,"mobile.driver.agree.btn"
+100. Click Get Started,tap,,"mobile.driver.get_started.btn"
+101.Click Next,tap,,"mobile.driver.next.btn"
+102.Click Mobile Number,tap,,"mobile.driver.mobile_number_field.btn"
+103.Click Close,tap,,"mobile.driver.cancel.btn"
+104. Enter Mobile Number,type,{autoPhone},"mobile.driver.edit_text.input"
+105.Wait for Continue,wait_until_visible,,"mobile.driver.continue.btn"
+106.Click Continue,tap,,"mobile.driver.continue.btn"
+107.Enter OTP,type,123456,"mobile.driver.edit_text.input"
+108.Enter Account Holder,type,{autoName},"mobile.driver.bank_details.account_holder_name"
+109.Enter Account Number,type,50100123456789,"mobile.driver.bank_details.account_number"
+110.Enter Confirm Account Number,type,50100123456789,"mobile.driver.bank_details.confirm_account_number"
+111.Enter IFSC Code,type,HDFC0001234,"mobile.driver.bank_details.confirm_ifsc_code"
+112.Wait For Keyboard Minimises,hide_keyboard,,
+113.Enter Upi Id,type,sujanpariyar07@fam,"mobile.driver.bank_details.upi_id"
+114.Wait For Keyboard Minimises,hide_keyboard,,
+115.Click Submit,click,,"mobile.driver.bank_details.submit_btn"
+116.Force Driver Location To Perambur,set_location,13.121030;80.232578,
+117.Click Allow Location,tap,,"mobile.driver.location_allow.btn"
+118.Wait for Toast to Hide,wait,3000,,
+119.Click Select All Agree,tap,,"mobile.driver.independent_contractor.checkbox_Select_All"
+120.Wait for Agree,wait_until_visible,,"mobile.driver.agree_continue.btn"
+121.Click Agree,tap,,"mobile.driver.agree_continue.btn"
+122.Wait For OTP,wait_until_visible,,"mobile.driver.edit_text.input"
+123. Enter OTP,type,123456,"mobile.driver.edit_text.input"
+124. Wait For Driver App,wait_until_visible,,"mobile.driver.app_header.label"
+125.Wait For Hamburger Menu,wait,3000
+126.Click Online Toggle,tap_coordinate ,975:1935,COORDINATE_MODE
+126. Load User App,switch_to,user,
+127. Wait For Get Started,wait_until_visible,,"mobile.customer.get_started.btn"
+128.Click Get Started,tap,,"mobile.customer.get_started.btn"
+129.Click Allow Notification,tap,,"mobile.customer.permission_allow.btn"
+130.Force User Location To Perambur,set_location,13.121030;80.232578,
+131.Click Next,tap,,"mobile.customer.next.btn"
+132.Click Mobile Number,tap,,"mobile.customer.mobile_number_field.btn"
+133.Click Close,tap,,"mobile.customer.cancel.btn"
+134.Enter Mobile Number,type,{customerPhone},"mobile.customer.edit_text.input"
+135.Wait for Continue,wait_until_visible,,"mobile.customer.continue.btn"
+136.Click Continue,tap,,"mobile.customer.continue.btn"
+137.Enter OTP,type,123456,"mobile.customer.otp_input"
+138.Wait for Finish,wait_until_visible,,"mobile.customer.finish.btn"
+139.Click Finish,tap,,"mobile.customer.finish.btn"
+140.Click Allow Location,tap,,"mobile.customer.location_allow.btn"
+141.Wait For Auto Ride,wait_until_visible,,"mobile.customer.auto_ride.btn"
+142.Click Auto Ride,tap,,"mobile.customer.auto_ride.btn"
+143.Enter Destination,type,Parsn Manare,"mobile.customer.destination.input"
+144.Wait for Location,wait_until_visible,,"mobile.customer.set_location_map.btn"
+145.Select Destination,tap,,"mobile.customer.destination_suggestion_first"
+146.Wait For Entrance,wait_until_visible,,"mobile.customer.destination_entrance_location"
+147.Click Entrance,tap,,"mobile.customer.destination_entrance_location"
+148.Click Confirm,tap,,"mobile.customer.confirm.btn"
+149.Wait For Ride,wait,5000,
+150.Wait for Ride,wait_until_visible,,"mobile.customer.ride_now.btn"
+151.Ride Now,tap,,"mobile.customer.ride_now.btn"
+152.Load Driver App,switch_to,driver,
+153.Wait for Accept,wait_until_visible,,"mobie.driver.auto_ride_accept.button"
+154.Click  Accept Ride,tap,,"mobie.driver.auto_ride_accept.button"
+155.Load User App,switch_to,user,
+156.Wait for OTP Layout to Load,wait_until_visible,,"mobile.customer.otp_display_element"
+157.Extract OTP from Screen,store_text,ride_otp,"mobile.customer.otp_display_element"
+158.Wait for load,wait,2000,
+159.Click SOS button,tap,,"mobile.customer.ride.sos_btn"
+160.Wait For Popup,wait,3000,
+161.Click Police bttuon,tap,,"mobile.customer.ride.sos_btn.police_btn"
+162.Click Call Button,tap,,"mobile.customer.ride.sos_btn.police.call_btn"
+163.Wait for Call Placement,wait,3000,
+164. Load Driver App,switch_to,driver,
+165.Wait for On My Way,wait_until_visible,,"mobile.driver.on_my_way.btn"
+166.Wait for Arrived,wait_until_visible,,"mobile.driver.arrived.btn"
+167.Wait for Arrived,wait_until_visible,,"mobile.driver.arrived.btn"
+168.Ride Arrived,tap,,"mobile.driver.arrived.btn"
+169.Wait for Yes,wait_until_visible,,"mobile.driver.yes.btn"
+170.Yes Arrived,tap,,"mobile.driver.yes.btn"
+171.Wait for Start Ride,wait_until_visible,,"mobile.driver.start_ride.btn"
+172.Start Ride,tap,,"mobile.driver.start_ride.btn"
+173.wait for Otp,wait_until_visible,,"mobile.driver.otp_view.input"
+174.Enter  Extracted OTP,type,{ride_otp},"mobile.driver.otp_view.input"
+175.Wait for Start Button,wait_until_visible,,"mobile.driver.start.btn"
+176.Start Ride Button,tap,,"mobile.driver.start.btn"
+177.wait for data,wait,3000,
+178.Click SOS Button,tap_coordinate ,972:1207,COORDINATE_MODE
+179.Wait For Popup,wait,3000,
+180.Click Police Button,tap,,"mobile.driver.ride.sos.call_108"
+181.Click Call Button,tap,,"mobile.driver.ride.sos.call_btn"
+182.Wait for Phone Dialer,wait,3000,
+183. Switch To Web,switch_to,web,
+184. Click Dashboard,Click,,"web.global.menu.dashboard"
+185. Click Setting,click,,"admin.setting.sidebar.menu"
+186. Click Panic call setting,click,,"admin.setting.panic_call.sidebar_menu"
+187. Search name,type,{policeName},"admin.setting.panic_call.search_name"
+188.Wait For Load,wait,1000,
+189. Delete Panic Call Delete,click,,"admin.setting.panic_call.delete_btn"
+190. Confirm Delete,click,,"admin.setting.panic_call.confirm_delete_btn"
+191. Wait For Delete,wait,2000,</t>
   </si>
 </sst>
 </file>
@@ -1238,8 +1432,8 @@
     <col min="6" max="6" width="45.77734375" customWidth="1"/>
     <col min="7" max="7" width="71.44140625" customWidth="1"/>
     <col min="8" max="8" width="40.44140625" customWidth="1"/>
-    <col min="9" max="9" width="61.88671875" customWidth="1"/>
-    <col min="10" max="10" width="32.88671875" customWidth="1"/>
+    <col min="9" max="9" width="34.21875" customWidth="1"/>
+    <col min="10" max="10" width="60.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
@@ -1294,7 +1488,7 @@
         <v>32</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>10</v>
@@ -1302,7 +1496,9 @@
       <c r="I2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="J2" s="2"/>
+      <c r="J2" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>

--- a/EPIC_0005_Ride_Safety_Calls.xlsx
+++ b/EPIC_0005_Ride_Safety_Calls.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Framework_For_WE1_Automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DA09093-C24C-41B6-9D53-2F8A5FA003D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7F3E865-6234-4FC0-8988-CC0641F890D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/EPIC_0005_Ride_Safety_Calls.xlsx
+++ b/EPIC_0005_Ride_Safety_Calls.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Framework_For_WE1_Automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7F3E865-6234-4FC0-8988-CC0641F890D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6F86D87-A0CF-48F9-B4DE-B8F32A3CFB8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -411,13 +411,7 @@
     <t xml:space="preserve">Admin Web portal is accessible and Cutomer App is availbale in emulator </t>
   </si>
   <si>
-    <t>TC_RG_01_Emergency_Calls</t>
-  </si>
-  <si>
     <t>Panic Call Check</t>
-  </si>
-  <si>
-    <t>TC_RG_02_Panic_Call</t>
   </si>
   <si>
     <t>1. Reload the User App completely.
@@ -880,6 +874,12 @@
 189. Delete Panic Call Delete,click,,"admin.setting.panic_call.delete_btn"
 190. Confirm Delete,click,,"admin.setting.panic_call.confirm_delete_btn"
 191. Wait For Delete,wait,2000,</t>
+  </si>
+  <si>
+    <t>TC_RG_02_Emergency_Calls</t>
+  </si>
+  <si>
+    <t>TC_RG_03_Panic_Call</t>
   </si>
 </sst>
 </file>
@@ -1381,7 +1381,7 @@
         <v>20</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>25</v>
@@ -1473,31 +1473,31 @@
         <v>19</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="F2" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">

--- a/EPIC_0005_Ride_Safety_Calls.xlsx
+++ b/EPIC_0005_Ride_Safety_Calls.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Framework_For_WE1_Automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6F86D87-A0CF-48F9-B4DE-B8F32A3CFB8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{344E7EDC-4E79-4F21-8C02-658F12A79A98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UserDriverWebIntialilzer" sheetId="43" r:id="rId1"/>
     <sheet name="CustomerAppEmergencyNumber" sheetId="48" r:id="rId2"/>
     <sheet name="PanicCallCheck" sheetId="49" r:id="rId3"/>
+    <sheet name="RideAerialViewEarningReports" sheetId="50" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="46">
   <si>
     <t>Requirement Title</t>
   </si>
@@ -880,6 +881,831 @@
   </si>
   <si>
     <t>TC_RG_03_Panic_Call</t>
+  </si>
+  <si>
+    <t>Test Case Using Regression Driver And Customer</t>
+  </si>
+  <si>
+    <t>Driver Onboarding</t>
+  </si>
+  <si>
+    <t>This test case validates the end-to-end booking, fulfillment, and backend audit flow for an Auto Ride service across the User App, Driver App, and Super Admin Web Portal. It covers logging in both the driver and customer with forced locations in Perambur, initiating an "Auto Ride" to "Parsn Manere", and verifying real-time driver tracking via the Admin Aerial View across booking, pickup, and ongoing trip stages. It also validates dynamic OTP extraction, trip completion, cash payment settlement, mutual user-driver ratings, and back-office administrative tasks including review approval and transaction settlement in the earning reports.</t>
+  </si>
+  <si>
+    <t>1. Open Driver App session.
+2.Wait for notification permissions dialog to appear.
+3.Grant notification permissions when prompted.
+4. Set driver location to Perambur (13.121030, 80.232578).
+5. Accept the terms and agreements screen.
+6. Tap "Get Started" on the onboarding screen.
+7. Tap "Next" to navigate through onboarding.
+8. Tap the Mobile Number input field.
+9. Dismiss any system auto-fill popups or dialogs.
+10. Enter the approved driver mobile number.
+11. Wait for the Continue button to become visible.
+12. Tap "Continue".
+13. Enter the verification OTP (123456).
+14. Grant location permissions for the Driver App.
+15. Confirm reaching the Driver App header/landing page.
+16. Wait to ensure the online toggle status is ON.
+17. Switch to the Super Admin Web Portal.
+18. Click on "Dashboard" from the navigation menu.
+19. Click on "Transport Service" module.
+20. Click the Search Box.
+21. Search for "Auto Ride" in services.
+22. Click the Home Icon.
+23. Click on the "Aerial View" tab.
+24. Click "All" to filter drivers in aerial view.
+25. Wait for aerial view map data to load.
+26. Re-click "Aerial View" tab if required to refresh.
+27. Click "Available" filter button.
+28. Search for the driver ("regression approved driver").
+29. Wait for driver marker/details to appear on map.
+30. Click "Back" button on aerial view dashboard.
+31. Switch to the User App session.
+32. Wait for onboarding screen to load.
+33. Tap "Get Started" on the onboarding screen.
+34. Grant notification permissions when prompted.
+35. Set mock/forced user location to Perambur (13.121030, 80.232578).
+36. Tap "Next" on the onboarding screen.
+37. Tap the Mobile Number input field.
+38. Dismiss any system auto-fill popups or dialogs.
+39. Enter the customer mobile number.
+40. Wait for Continue button to appear.
+41. Tap "Continue".
+42. Enter the verification OTP (123456).
+43. Wait for Finish button to appear.
+44. Tap "Finish" to complete login.
+45. Grant location permissions for the User App.
+46. Wait for "Auto Ride" option to load.
+47. Select "Auto Ride" from the ride options.
+48. Enter the destination ("Parsn Manare") into the search field.
+49. Wait for location pin/map UI to appear.
+50. Select the first matching destination suggestion from the list.
+51. Wait for entrance location options to load.
+52. Select the entrance location on the map.
+53. Tap "Confirm" to proceed with the selected pickup/drop location.
+54. Wait for system to process location.
+55. Wait for "Ride Now" button to become visible.
+56. Tap "Ride Now" to broadcast the ride request.
+57. Switch to the Driver App session.
+58. Wait for incoming ride request pop-up.
+59. Accept the incoming ride request pop-up.
+60. Switch to the User App session.
+61. Wait for the OTP layout/display element to load.
+62. Note down/extract the displayed Ride OTP.
+63. Switch to the Super Admin Web Portal.
+64. Click on the "Aerial View" tab.
+65. Click "Enroute to Pickup" filter button.
+66. Search for the assigned driver ("regression approved driver").
+67. Wait for filtered driver details to load.
+68. Click the Eye icon to inspect driver details and real-time tracking.
+69. Wait for live aerial view streaming map to render.
+70. Click "Back" button to return to main aerial view list.
+71. Switch to the Driver App session.
+72. Wait for "On My Way" status update.
+73. Wait for "Arrived" button to become visible.
+74. Confirm arrival button visibility.
+75. Tap "Arrived" once reaching the pickup location.
+76. Wait for arrival confirmation popup.
+77. Tap "Yes" on the arrival confirmation dialog.
+78. Switch to the Super Admin Web Portal.
+79. Click on the "Aerial View" tab.
+80. Click "Reached Pickup" filter button.
+81. Search for the assigned driver ("regression approved driver").
+82. Wait for filtered driver details to load.
+83. Click the Eye icon to view driver status.
+84. Wait for aerial map view to render.
+85. Click "Back" button to return.
+86. Switch to the Driver App session.
+87. Wait for "Start Ride" button to appear.
+88. Tap "Start Ride".
+89. Wait for OTP verification input box.
+90. Enter the extracted Ride OTP into the verification input field.
+91. Wait for "Start" button to activate.
+92. Tap "Start" to officially begin the trip.
+93. Switch to the Super Admin Web Portal.
+94. Click on the "Aerial View" tab.
+95. Click "Ongoing" ride filter button.
+96. Search for the assigned driver ("regression approved driver").
+97. Wait for driver results to populate.
+98. Click the Eye icon to view ongoing trip status on map.
+99. Wait for live trip route map view to load.
+100. Click Close button on the Eye icon tracking overlay modal.
+101. Switch to the Driver App session.
+102. Wait for "Complete Ride" button to appear.
+103. Tap "Complete Ride" upon reaching the destination.
+104. Wait for "Collect Payment" button to appear.
+105. Tap "Collect Payment" to initiate the cash settlement flow.
+106. Switch to the User App session.
+107. Wait for "Proceed to Pay" button to load on screen.
+108. Tap "Proceed to Pay" on the payment screen.
+109. Wait for payment confirmation screen.
+110. Select "Pay Cash" / confirm cash payment choice.
+111. Wait for Review screen to load.
+112. Tap "Give Review".
+113. Select the star rating by tapping the rating bar.
+114. Tap "Submit Rating".
+115. Wait for "Done" button to appear.
+116. Tap "Done" to finish the trip flow on the customer side.
+117. Switch to the Driver App session.
+118. Wait for Payment Proceed button to appear.
+119. Tap "Proceed" on the payment verification screen.
+120. Wait for confirmation dialog.
+121. Tap "Yes" to confirm receipt of the cash payment.
+122. Wait for "Give Review" button to load.
+123. Tap "Give Review".
+124. Wait for star rating options to load.
+125. Select the star rating for the customer.
+126. Tap "Submit Rating".
+127. Wait for "Complete" button to appear.
+128. Tap "Complete" to navigate to summary view.
+129. Wait for final "Ride Complete Submit" button.
+130. Tap "Submit" to finalize and clear the completed ride from driver portal.
+131. Switch to the Super Admin Web Portal.
+132. Click on "Reviews" menu from transport management navigation.
+133. Wait for reviews grid/table to load.
+134. Click "Today" statistics filter button.
+135. Wait for today's statistics data to update.
+136. Click "Search" button in reviews filter bar.
+137. Wait for search results grid to load.
+138. Filter grid by Customer Name ("regression customer name").
+139. Wait for customer filter to apply.
+140. Filter grid by Driver Name ("regression driver name").
+141. Wait for driver filter to apply.
+142. Click "Approve" (Thumbs Up) button to approve the review.
+143. Wait for approval request to finish processing.
+144. Click "Today" statistics filter button to refresh overview.
+145. Click "Earning Report" menu option.
+146. Click "Today" statistics filter button on earnings page.
+147. Wait for today's financial summary to load.
+148. Click "Search" button on reports page.
+149. Wait for earning reports table to populate.
+150. Scroll table grid horizontally to reach payment status column.
+151. Wait for table layout adjustment.
+152. Filter records by Customer Name.
+153. Wait for customer records to update.
+154. Filter records by Driver Name.
+155. Wait for driver records to update.
+156. Scroll grid horizontally to locate payment status controls.
+157. Enter "Unsettled" in the payment status filter field.
+158. Wait for list to filter down to unsettled records.
+159. Select the specific Unsettled Ride record.
+160. Wait for transaction action options to appear.
+161. Click "Settle Transaction" (Mark as Settle) button.
+162. Wait for financial settlement processing to complete.</t>
+  </si>
+  <si>
+    <t>Admin Web portal is accessible and the logged-in admin user has permission to access site settings</t>
+  </si>
+  <si>
+    <t>1.Reload User App Completely,reload_app,user,
+2.Reload Driver App Completely,reload_app,driver,
+3.Load Driver App,switch_to,driver,
+4.Wait For Notification,wait_until_visible,,"mobile.driver.permission_allow.btn"
+5.Click Allow Notification,tap,,"mobile.driver.permission_allow.btn"
+6.Force Driver Location To Perambur,set_location,13.121030;80.232578,
+7.Click Agree,tap,,"mobile.driver.agree.btn"
+8.Click Get Started,tap,,"mobile.driver.get_started.btn"
+9.Click Next,tap,,"mobile.driver.next.btn"
+10.Click Mobile Number,tap,,"mobile.driver.mobile_number_field.btn"
+11.Click Close,tap,,"mobile.driver.cancel.btn"
+12.Enter Mobile Number,type,regression.approved_driver.phone,"mobile.driver.edit_text.input"
+13.Wait for Continue,wait_until_visible,,"mobile.driver.continue.btn"
+14.Click Continue,tap,,"mobile.driver.continue.btn"
+15.Enter OTP,type,123456,"mobile.driver.edit_text.input"
+16.Click Allow Location,tap,,"mobile.driver.location_allow.btn"
+17.Wait For Driver App,wait_until_visible,,"mobile.driver.app_header.label"
+18.Wait For Driver App Toggle On,wait,3000,
+19.Load Super Admin,switch_to,web,
+21.Click Dashboard,Click,,"web.global.menu.dashboard"
+22.Click Transport Service,Click,,"web.global.transport_service.menu"
+23.Click Search Box,click,,"web.global.transport_service.search.input"
+24.Enter Services,type,Auto Ride,"web.global.transport_service.search.input"
+25.Click Home Icon,Click,,"web.global.transport_service.home.icon"
+26.Click AerialView Button,click,,"admin.transport_service.areial_view.tab"
+27.Click All Button,click,,"admin.transport_service.areial_view.all.button"
+28.Wait For Load,wait,2000,
+29.Click AerialView Button,click,,"admin.transport_service.areial_view.tab"
+30.Click available button,click,,"admin.transport_service.areial_view.available.button"
+31.Search Driver,type,regression approved driver,"admin.transport.aerial_view.driver_search_field"
+32.Wait For Driver,wait,2000,
+33.Click Eye Button,click,,"admin.transport_service.areial_view.eye.button"
+34.Wait For Aerial View,wait,5000,
+35.Click Back Button,click,,"admin.transport_service.areial_view.back.button"
+36.Load User App,switch_to,user,
+37.Wait For Get Started,wait_until_visible,,"mobile.customer.get_started.btn"
+38.Click Get Started,tap,,"mobile.customer.get_started.btn"
+39.Click Allow Notification,tap,,"mobile.customer.permission_allow.btn"
+40.Force User Location To Perambur,set_location,13.121030;80.232578,
+41.Click Next,tap,,"mobile.customer.next.btn"
+42.Click Mobile Number,tap,,"mobile.customer.mobile_number_field.btn"
+43.Click Close,tap,,"mobile.customer.cancel.btn"
+44.Enter Mobile Number,type,regression.customer.phone,"mobile.customer.edit_text.input"
+45.Wait for Continue,wait_until_visible,,"mobile.customer.continue.btn"
+46. Click Continue,tap,,"mobile.customer.continue.btn"
+47. Enter OTP,type,123456,"mobile.customer.otp_input"
+48. Wait for Finish,wait_until_visible,,"mobile.customer.finish.btn"
+49. Click Finish,tap,,"mobile.customer.finish.btn"
+50. Click Allow Location,tap,,"mobile.customer.location_allow.btn"
+51. Wait For Auto Ride,wait_until_visible,,"mobile.customer.auto_ride.btn"
+52.Click Auto Ride,tap,,"mobile.customer.auto_ride.btn"
+53.Enter Destination,type,Parsn Manare,"mobile.customer.destination.input"
+54.Wait for Location,wait_until_visible,,"mobile.customer.set_location_map.btn"
+55.Select Destination,tap,,"mobile.customer.destination_suggestion_first"
+56.Wait For Entrance,wait_until_visible,,"mobile.customer.destination_entrance_location"
+57.Click Entrance,tap,,"mobile.customer.destination_entrance_location"
+58. Click Confirm,tap,,"mobile.customer.confirm.btn"
+59.Wait For Ride,wait,5000,
+60.Wait for Ride,wait_until_visible,,"mobile.customer.ride_now.btn"
+61.Ride Now,tap,,"mobile.customer.ride_now.btn"
+62.Load Driver App,switch_to,driver,
+63.Wait for Accept,wait_until_visible,,"mobie.driver.auto_ride_accept.button"
+64.Click  Accept Ride,tap,,"mobie.driver.auto_ride_accept.button"
+65.Load User App,switch_to,user,
+66.Wait for OTP Layout to Load,wait_until_visible,,"mobile.customer.otp_display_element"
+67.Extract OTP from Screen,store_text,ride_otp,"mobile.customer.otp_display_element"
+68.Switch to web,switch_to,web,
+69.Click AerialView Button,click,,"admin.transport_service.areial_view.tab"
+70.Click Enroute to pickup,click,,"admin.transport_service.areial_view.enroute_to_pickup.button"
+71.Search Driver,type,regression approved driver,"admin.transport.aerial_view.driver_search_field"
+72.Wait For Driver,wait,2000,
+73.Click Eye Button,click,,"admin.transport_service.areial_view.eye.button"
+74.Wait For Aerial View,wait,5000,
+75.Click Back Button,click,,"admin.transport_service.areial_view.back.button"
+76.Load Driver App,switch_to,driver,
+77.Wait for On My Way,wait_until_visible,,"mobile.driver.on_my_way.btn"
+78.Wait for Arrived,wait_until_visible,,"mobile.driver.arrived.btn"
+79.Wait for Arrived,wait_until_visible,,"mobile.driver.arrived.btn"
+80.Ride Arrived,tap,,"mobile.driver.arrived.btn"
+81.Wait for Yes,wait_until_visible,,"mobile.driver.yes.btn"
+82.Yes Arrived,tap,,"mobile.driver.yes.btn"
+83.Switch to web,switch_to,web,
+84.Click AerialView Button,click,,"admin.transport_service.areial_view.tab"
+85.Click Reached Pickup,click,,"admin.transport_service.areial_view.reached_pickup.button"
+86.Search Driver,type,regression approved driver,"admin.transport.aerial_view.driver_search_field"
+87.Wait For Driver,wait,2000,
+88.Click Eye Button,click,,"admin.transport_service.areial_view.eye.button"
+89.Wait For Aerial View,wait,5000,
+90.Click Back Button,click,,"admin.transport_service.areial_view.back.button"
+91.Load Driver App,switch_to,driver,
+92.Wait for Start Ride,wait_until_visible,,"mobile.driver.start_ride.btn"
+93.Start Ride,tap,,"mobile.driver.start_ride.btn"
+94.wait for Otp,wait_until_visible,,"mobile.driver.otp_view.input"
+95.Enter  Extracted OTP,type,{ride_otp},"mobile.driver.otp_view.input"
+96.Wait for Start Button,wait_until_visible,,"mobile.driver.start.btn"
+97.Start Ride Button,tap,,"mobile.driver.start.btn"
+98.Swtich To Web,switch_to,user,
+99.Click AerialView Button,click,,"admin.transport_service.areial_view.tab"
+100.Click Ongoing Button,click,,"admin.transport_service.areial_view.ongoing.button"
+101.Search Driver,type,regression approved driver,"admin.transport.aerial_view.driver_search_field"
+102.Wait For Driver,wait,2000,
+103.Click Eye Button,click,,"admin.transport_service.areial_view.eye.button"
+104.Wait For Aerial View,wait,5000,
+105.Load Driver App,switch_to,driver,
+106.Wait for Complete Ride,wait_until_visible,,"mobile.driver.complete_ride.btn"
+107.Complete Ride,tap,,"mobile.driver.complete_ride.btn"
+108.Wait for Collect Payment,wait_until_visible,,"mobile.driver.collect_payment.btn" 
+109.Collect Payment,tap,,"mobile.driver.collect_payment.btn"
+110.Load User App,switch_to,user,
+111.Wait for Proceed Payment,wait_until_visible,,"mobile.customer.proceed_to_pay.btn"
+112.Proceed Payment,tap,,"mobile.customer.proceed_to_pay.btn"
+113.Wait for Proceed Pay Confirm,wait_until_visible,,"mobile.customer.proceed_to_pay.btn"
+114.Pay Cash,tap,,"mobile.customer.proceed_to_pay.btn"
+115.Wait for Review,wait_until_visible,,"mobile.customer.give_review.btn"
+116.Give Review,tap,,"mobile.customer.give_review.btn"
+117.Give Rating,tap_coordinate,348:1619,
+118.Submit Rating,tap,,"mobile.customer.submit_rating.btn"
+119.Wait for Done,wait_until_visible,,"mobile.customer.done.btn"
+120.Trip Finished,tap,,"mobile.customer.done.btn"
+121.Load Driver App,switch_to,driver,
+122.Wait  For Proceed,wait_until_visible,,"mobile.driver.payment.proceed_btn"
+123.Click For Proceed,tap,,"mobile.driver.payment.proceed_btn"
+124.Wait for Yes,wait_until_visible,,"mobile.driver.yes.btn"
+125.Confirm Payment,tap,,"mobile.driver.yes.btn"
+126.Wait For Give Review Button,wait_until_visible,,"mobile.driver.give_review.btn"
+127.Click Give Review Button,tap,,"mobile.driver.give_review.btn"
+128.Wait For Rating,wait,2000,
+129.Give Rating,tap_coordinate,348:1545,
+130.Submit Rating,tap,,"mobile.driver.submit_rating.btn"
+131.Wait for Complete Button,wait_until_visible,,"mobile.driver.complete.btn"
+132.Click Complete Button,tap,,"mobile.driver.complete.btn"
+133.Wait For  ride complete submit button,wait_until_visible,,"mobile.driver.ride_complete_submit.btn"
+134.Click Ride Complete Submit Button,tap,,"mobile.driver.ride_complete_submit.btn"
+135.Switch to Web,switch_to,web,
+136.Click Review Menu,click,,"admin.transport.reviews.top_menu_btn"
+137.Wait For Review,wait,1000,
+138.Click Today Button,Click,,"web.global.dashboard.today_statistics"
+139.Wait For Today Statistics,wait,2000,
+140.Click Search Button,click,,"admin.transport.reviews.search_btn"
+141.Wait For Load,wait,2000,
+142.Filter Customer Name List,type,regression.customer.name,"admin.transport.reviews.customer_filter_name"
+143.Wait For Loading,wait,1000,
+144.Filter Driver Name List,type,regression.approved_driver.name,"admin.transport.reviews.driver_filter_name"
+145.Wait For Loading,wait,1000,
+146.Click Thumb Up,click,,"admin.transport.reviews.approve_btn"
+147.Wait For Loading,wait,3000,
+148.Click Earning Report,click,,"admin.transport.earning_reports.top_menu_btn"
+149.Click Today Button,Click,,"web.global.dashboard.today_statistics"
+150.Wait For Today Statistics,wait,2000,
+151.Click Search Button,click,,"admin.transport.reviews.search_btn"
+152.Wait For Load,wait,2000,
+153.Filter Customer Name List,type,regression.customer.name,"admin.transport.reviews.customer_filter_name"
+154.Wait For Loading,wait,1000,
+155.Filter Driver Name List,type,regression.approved_driver.name,"admin.transport.reviews.driver_filter_name"
+156.Wait For Loading,wait,1000,
+157.Scroll Grid,tab,28,"admin.transport.earning_reports.payment_status_filter"
+158.Select Ride To Settle,click,,"admin.transport.earning_reports.ride_to_settle_select"
+159.Click Settle Transaction Button,click,"admin.transport.earning_reports.mark_as_settle_btn"</t>
+  </si>
+  <si>
+    <t>1.Reload User App Completely,reload_app,user,
+2.Reload Driver App Completely,reload_app,driver,
+3.Load Driver App,switch_to,driver,
+4.Wait For Notification,wait_until_visible,,"mobile.driver.permission_allow.btn"
+5.Click Allow Notification,tap,,"mobile.driver.permission_allow.btn"
+6.Force Driver Location To Perambur,set_location,13.121030;80.232578,
+7.Click Agree,tap,,"mobile.driver.agree.btn"
+8.Click Get Started,tap,,"mobile.driver.get_started.btn"
+9.Click Next,tap,,"mobile.driver.next.btn"
+10.Click Mobile Number,tap,,"mobile.driver.mobile_number_field.btn"
+11.Click Close,tap,,"mobile.driver.cancel.btn"
+12.Enter Mobile Number,type,regression.approved_driver.phone,"mobile.driver.edit_text.input"
+13.Wait for Continue,wait_until_visible,,"mobile.driver.continue.btn"
+14.Click Continue,tap,,"mobile.driver.continue.btn"
+15.Enter OTP,type,123456,"mobile.driver.edit_text.input"
+16.Click Allow Location,tap,,"mobile.driver.location_allow.btn"
+17.Wait For Driver App,wait_until_visible,,"mobile.driver.app_header.label"
+18.Wait For Driver App Toggle On,wait,3000,
+19.Load Super Admin,switch_to,web,
+20.Click Dashboard,Click,,"web.global.menu.dashboard"
+21.Click Transport Service,Click,,"admin.transport.menu.card"
+22.Click Search Box,click,,"admin.transport.search.input_box"
+23.Enter Services,type,Auto Ride,"admin.transport.search.input_box"
+24.Click Home Icon,Click,,"admin.transport.home.icon"
+25.Click AerialView Button,click,,"admin.transport_service.areial_view.tab"
+26.Click All Button,click,,"admin.transport_service.areial_view.all.button"
+27.Wait For Load,wait,2000,
+28.Click AerialView Button,click,,"admin.transport_service.areial_view.tab"
+29.Click available button,click,,"admin.transport_service.areial_view.available.button"
+30.Search Driver,type,regression approved driver,"admin.transport.aerial_view.driver_search_field"
+31.Wait For Driver,wait,2000,
+32.Click Back Button,click,,"admin.transport_service.areial_view.back.button"
+33.Load User App,switch_to,user,
+34.Wait For Get Started,wait_until_visible,,"mobile.customer.get_started.btn"
+35.Click Get Started,tap,,"mobile.customer.get_started.btn"
+36.Click Allow Notification,tap,,"mobile.customer.permission_allow.btn"
+37.Force User Location To Perambur,set_location,13.121030;80.232578,
+38.Click Next,tap,,"mobile.customer.next.btn"
+39.Click Mobile Number,tap,,"mobile.customer.mobile_number_field.btn"
+40.Click Close,tap,,"mobile.customer.cancel.btn"
+41.Enter Mobile Number,type,regression.customer.phone,"mobile.customer.edit_text.input"
+42.Wait for Continue,wait_until_visible,,"mobile.customer.continue.btn"
+43. Click Continue,tap,,"mobile.customer.continue.btn"
+44. Enter OTP,type,123456,"mobile.customer.otp_input"
+45. Wait for Finish,wait_until_visible,,"mobile.customer.finish.btn"
+46. Click Finish,tap,,"mobile.customer.finish.btn"
+47. Click Allow Location,tap,,"mobile.customer.location_allow.btn"
+48. Wait For Auto Ride,wait_until_visible,,"mobile.customer.auto_ride.btn"
+49.Click Auto Ride,tap,,"mobile.customer.auto_ride.btn"
+50.Enter Destination,type,Parsn Manare,"mobile.customer.destination.input"
+51.Wait for Location,wait_until_visible,,"mobile.customer.set_location_map.btn"
+52.Select Destination,tap,,"mobile.customer.destination_suggestion_first"
+53.Wait For Entrance,wait_until_visible,,"mobile.customer.destination_entrance_location"
+54.Click Entrance,tap,,"mobile.customer.destination_entrance_location"
+55. Click Confirm,tap,,"mobile.customer.confirm.btn"
+56.Wait For Ride,wait,5000,
+57.Wait for Ride,wait_until_visible,,"mobile.customer.ride_now.btn"
+58.Ride Now,tap,,"mobile.customer.ride_now.btn"
+59.Load Driver App,switch_to,driver,
+60.Wait for Accept,wait_until_visible,,"mobie.driver.auto_ride_accept.button"
+61.Click  Accept Ride,tap,,"mobie.driver.auto_ride_accept.button"
+62.Load User App,switch_to,user,
+63.Wait for OTP Layout to Load,wait_until_visible,,"mobile.customer.otp_display_element"
+64.Extract OTP from Screen,store_text,ride_otp,"mobile.customer.otp_display_element"
+65.Switch to web,switch_to,web,
+66.Click AerialView Button,click,,"admin.transport_service.areial_view.tab"
+67.Click Enroute to pickup,click,,"admin.transport_service.areial_view.enroute_to_pickup.button"
+68.Search Driver,type,regression approved driver,"admin.transport.aerial_view.driver_search_field"
+69.Wait For Driver,wait,2000,
+70.Click Eye Button,click,,"admin.transport_service.areial_view.eye.button"
+71.Wait For Aerial View,wait,5000,
+72.Click Back Button,click,,"admin.transport_service.areial_view.back.button"
+73.Load Driver App,switch_to,driver,
+74.Wait for On My Way,wait_until_visible,,"mobile.driver.on_my_way.btn"
+75.Wait for Arrived,wait_until_visible,,"mobile.driver.arrived.btn"
+76.Wait for Arrived,wait_until_visible,,"mobile.driver.arrived.btn"
+77.Ride Arrived,tap,,"mobile.driver.arrived.btn"
+78.Wait for Yes,wait_until_visible,,"mobile.driver.yes.btn"
+79.Yes Arrived,tap,,"mobile.driver.yes.btn"
+80.Switch to web,switch_to,web,
+81.Click AerialView Button,click,,"admin.transport_service.areial_view.tab"
+82.Click Reached Pickup,click,,"admin.transport_service.areial_view.reached_pickup.button"
+83.Search Driver,type,regression approved driver,"admin.transport.aerial_view.driver_search_field"
+84.Wait For Driver,wait,2000,
+85.Click Eye Button,click,,"admin.transport_service.areial_view.eye.button"
+86.Wait For Aerial View,wait,5000,
+87.Click Back Button,click,,"admin.transport_service.areial_view.back.button"
+88.Load Driver App,switch_to,driver,
+89.Wait for Start Ride,wait_until_visible,,"mobile.driver.start_ride.btn"
+90.Start Ride,tap,,"mobile.driver.start_ride.btn"
+91.wait for Otp,wait_until_visible,,"mobile.driver.otp_view.input"
+92.Enter  Extracted OTP,type,{ride_otp},"mobile.driver.otp_view.input"
+93.Wait for Start Button,wait_until_visible,,"mobile.driver.start.btn"
+94.Start Ride Button,tap,,"mobile.driver.start.btn"
+95.Swtich To Web,switch_to,web,
+96.Click AerialView Button,click,,"admin.transport_service.areial_view.tab"
+97.Click Ongoing Button,click,,"admin.transport_service.areial_view.ongoing.button"
+98.Search Driver,type,regression approved driver,"admin.transport.aerial_view.driver_search_field"
+99.Wait For Driver,wait,2000,
+100.Click Eye Button,click,,"admin.transport_service.areial_view.eye.button"
+101.Wait For Aerial View,wait,5000,
+102.Click the closed Button,click,,"admin.transport.aerial_view.eye_icon_close"
+103.Load Driver App,switch_to,driver,
+104.Wait for Complete Ride,wait_until_visible,,"mobile.driver.complete_ride.btn"
+105.Complete Ride,tap,,"mobile.driver.complete_ride.btn"
+106.Wait for Collect Payment,wait_until_visible,,"mobile.driver.collect_payment.btn" 
+107.Collect Payment,tap,,"mobile.driver.collect_payment.btn"
+108.Load User App,switch_to,user,
+109.Wait for Proceed Payment,wait_until_visible,,"mobile.customer.proceed_to_pay.btn"
+110.Proceed Payment,tap,,"mobile.customer.proceed_to_pay.btn"
+111.Wait for Proceed Pay Confirm,wait_until_visible,,"mobile.customer.proceed_to_pay.btn"
+112.Pay Cash,tap,,"mobile.customer.proceed_to_pay.btn"
+113.Wait for Review,wait_until_visible,,"mobile.customer.give_review.btn"
+114.Give Review,tap,,"mobile.customer.give_review.btn"
+115.Give Rating,tap_coordinate,348:1619,
+116.Submit Rating,tap,,"mobile.customer.submit_rating.btn"
+117.Wait for Done,wait_until_visible,,"mobile.customer.done.btn"
+118.Trip Finished,tap,,"mobile.customer.done.btn"
+119.Load Driver App,switch_to,driver,
+120.Wait  For Proceed,wait_until_visible,,"mobile.driver.payment.proceed_btn"
+121.Click For Proceed,tap,,"mobile.driver.payment.proceed_btn"
+122.Wait for Yes,wait_until_visible,,"mobile.driver.yes.btn"
+123.Confirm Payment,tap,,"mobile.driver.yes.btn"
+124.Wait For Give Review Button,wait_until_visible,,"mobile.driver.give_review.btn"
+125.Click Give Review Button,tap,,"mobile.driver.give_review.btn"
+126.Wait For Rating,wait,2000,
+127.Give Rating,tap_coordinate,348:1545,
+128.Submit Rating,tap,,"mobile.driver.submit_rating.btn"
+129.Wait for Complete Button,wait_until_visible,,"mobile.driver.complete.btn"
+130.Click Complete Button,tap,,"mobile.driver.complete.btn"
+131.Wait For  ride complete submit button,wait_until_visible,,"mobile.driver.ride_complete_submit.btn"
+132.Click Ride Complete Submit Button,tap,,"mobile.driver.ride_complete_submit.btn"
+133.Switch to Web,switch_to,web,
+134.Click Review Menu,click,,"admin.transport.reviews.top_menu_btn"
+135.Wait For Review,wait,1000,
+136.Click Today Button,Click,,"web.global.dashboard.today_statistics"
+137.Wait For Today Statistics,wait,2000,
+138.Click Search Button,click,,"admin.transport.reviews.search_btn"
+139.Wait For Load,wait,2000,
+140.Filter Customer Name List,type,regression.customer.name,"admin.transport.reviews.customer_filter_name"
+141.Wait For Loading,wait,1000,
+142.Filter Driver Name List,type,regression.approved_driver.name,"admin.transport.reviews.driver_filter_name"
+143.Wait For Loading,wait,1000,
+144.Click Thumb Up,click,,"admin.transport.reviews.approve_btn"
+145.Wait For Loading,wait,3000,
+146.Click Today Button,Click,,"web.global.dashboard.today_statistics"
+147.Click Earning Report,click,,"admin.transport.earning_reports.top_menu_btn"
+148.Click Today Button,Click,,"web.global.dashboard.today_statistics"
+149.Wait For Today Statistics,wait,2000,
+150.Click Search Button,click,,"admin.report_issue.customer_report_issues.search_btn"
+151.Wait For Load,wait,2000,
+152.Scroll Grid,tab,6,"admin.transport.reviews.payment_status_filter_name"
+153.Wait For Load,wait,2000,
+154.Filter Customer Name List,type,regression.customer.name,"admin.transport.reviews.customer_filter_name"
+155.Wait For Loading,wait,1000,
+156.Filter Driver Name List,type,regression.approved_driver.name,"admin.transport.reviews.driver_filter_name"
+157.Wait For Loading,wait,1000,
+158.Scroll Grid,tab,23,"admin.transport.reviews.driver_filter_name"
+159.Enter Unsettled,type,unsettled,"admin.transport.earning_reports.payment_status_filter"
+160.Wait For Loading,wait,1000,
+161.Click Unsettled Ride,click,,"admin.transport.reviews.unsettled_ride"
+162.Wait For Loading,wait,1000,
+163.Click Settle Transaction Button,click,"admin.transport.earning_reports.mark_as_settle_btn"
+164.Wait For Loading,wait,4000,</t>
+  </si>
+  <si>
+    <t>TC_RG_04_Ride_Aerial_View</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Reload User App Completely,reload_app,user,
+2. Reload Driver App Completely,reload_app,driver,
+3. Load Driver App,switch_to,driver,
+4. Wait For Notification,wait_until_visible,,"mobile.driver.permission_allow.btn"
+5. Click Allow Notification,tap,,"mobile.driver.permission_allow.btn"
+6. Click Agree,tap,,"mobile.driver.agree.btn"
+7. Click Get Started,tap,,"mobile.driver.get_started.btn"
+8. Click Next,tap,,"mobile.driver.next.btn"
+9. Click Mobile Number Button,tap,,"mobile.customer.mobile_number_field.btn"
+10. Click Close,tap_if_present,,"mobile.driver.cancel.btn"
+11. Enter Mobile Number,type,{randomPhone}&gt;&gt;driverNumber,"mobile.driver.edit_text.input"
+12.Wait For Continue,wait_until_visible,,"mobile.driver.continue.btn"
+13.Click on Continue,tap,,"mobile.driver.continue.btn"
+14. wait for OTP,wait_until_visible,,"mobile.driver.edit_text.input"
+15. Enter OTP,type,123456,"mobile.driver.edit_text.input"
+16. Wait for Finish,wait_until_visible,,"mobile.driver.finish.btn"
+17. Click on Finish,tap,"mobile.driver.finish.btn"
+18.Wait For Profile Registation Page,wait_until_visible,"mobile.driver.Register.profile.pen_icon"
+19.Click on ProfileImage,tap,,"mobile.driver.Register.profile.pen_icon"
+20.Wait For Camera,wait_until_visible,"mobile.driver.Camera.btn"
+21.Click on camera,tap,,"mobile.driver.Camera.btn"
+22.Click while using this app Notification,tap,,"mobile.driver.camera_allow.btn"
+23.Click on Camera Icon,tap,,"mobile.driver.camera_selfie.btn"
+24.Click on Select Image,tap,,"mobile.driver.selfie_select.btn"
+25.Click on Crop Button,tap,,"mobile.driver.selfie_crop.btn"
+26.Type Driver Name,type,autoDriver{randomAlpha}&gt;&gt;driverName,"mobile.driver.driver_name_input"
+27.Enter Whatsapp Number,type,{randomPhone}&gt;&gt;whatsappNumber,"mobile.driver.whatsapp_no.input_box"
+28.Enter Email,type,{driverName}@gmail.com&gt;&gt;driverEmail,"mobile.driver.driver_email_input"
+29.Click  Gender Box Male,tap,,"mobile.driver.select_gender_male"
+30.Scroll Screen,swipe,up,
+31.Click  Social Media,tap,,"mobile.driver.how_did_you_hear_about_us"
+32.Select Instagram,tap,,"mobile.driver.select_option_instagram"
+33.Click Terms And Conditions,tap_coordinate ,124:1758,COORDINATE_MODE
+34.Click Sign Up,tap,,"mobile.driver.sign_up_btn"
+35.Wait For Vehicle Type,wait_until_visible,"mobile.driver.Service_vehicle_Type_heading"
+36.Select Auto Ride,tap,,"mobile.driver.select_auto_ride"
+37.Click Next,tap,,"mobile.driver.auto_ride_next_btn"
+38.Wait for Pop Up,wait_if_present,,"mobile.driver.driver_location_allow.btn"
+39.Click While Using This App Notification,tap_if_present,,"mobile.driver.driver_location_allow.btn"
+40.Click Upload image Icon,tap,,"mobile.driver.vehicle_image_upload_icon"
+41.Click on camera,tap,,"mobile.driver.Camera.btn"
+42.Click on Camera Icon,tap,,"mobile.driver.camera_selfie.btn"
+43.Click on Select Image,tap,,"mobile.driver.selfie_select.btn"
+44.Click on Crop Button,tap,,"mobile.driver.selfie_crop.btn"
+45.Click Select Vehicle Type Dropdown,tap,,"mobile.driver.vehicle_type_dropdown"
+46.Select Option Pink Auto,tap,,"mobile.driver.vehicle_type_option.pink_auto"
+47.Type Model Name,type,petrol,"mobile.driver.vehicle_model_name.input_box"
+48.Click Vehicle Model Year,tap,,"mobile.driver.vehicle_type_model_year.dropdown"
+49.Select Year,tap,,"mobile.driver.vehicle_type_model_year.option_year"
+50.Type Vehicle Plate No,type,TN22CL5170,"mobile.driver.Vehicle_plate_number"
+51.Click the Seat Number,tap,,"mobile.driver.select_seat_number.drop_down"
+52.Select Number Of Seat,tap,"mobile.driver.select_seat_number.option_three"
+53.Scroll Screen,swipe,up,
+54.Type Vehicle Color,type,Pink,"mobile.driver.Vehicle_colour"
+55.Save Vehicle Detaills,tap,,"mobile.drivers_vehicle_details.save_btn"
+56. Wait For Upload,wait_until_visible,,"mobile.driver.upload.btn"
+57. Click Upload,tap,,"mobile.driver.upload.btn"
+58. Upload License,tap,,"mobile.driver.upload_docs.btn"
+59.Click on camera,tap,,"mobile.driver.Camera.btn"
+60.Click on Camera Icon,tap,,"mobile.driver.camera_selfie.btn"
+61.Click on Select Image,tap,,"mobile.driver.selfie_select.btn"
+62.Click on Crop Button,tap,,"mobile.driver.selfie_crop.btn"
+63. Wait For Add Document,wait_until_visible,,"mobile.driver.add_documents.header"
+64. Click Calendar,tap_coordinate,121:1539,COORDINATE_MODE
+65. Click Month,tap,,"mobile.driver.next_month.btn"
+66. Click Date,tap_coordinate,943:1290,COORDINATE_MODE
+67. Click Ok,tap,,"mobile.driver.ok.btn"
+68. Click Upload Submission,tap,,"mobile.driver.upload_docs.btn"
+69.Click Next Button,tap,,"mobile.drivers.after_upload_doc.next_btn"
+70.Enter Account Holder,type,{driverName},"mobile.driver.bank_details.account_holder_name"
+71.Enter Account Number,type,50100123456789,"mobile.driver.bank_details.account_number"
+72.Enter Confirm Account Number,type,50100123456789,"mobile.driver.bank_details.confirm_account_number"
+73.Enter IFSC Code,type,HDFC0001234,"mobile.driver.bank_details.confirm_ifsc_code"
+74.Wait For Keyboard Minimises,hide_keyboard,,
+75.Enter Upi Id,type,sujanpariyar07@fam,"mobile.driver.bank_details.upi_id"
+76.Wait For Keyboard Minimises,hide_keyboard,,
+77.Click Submit,click,,"mobile.driver.bank_details.submit_btn"
+78.Wait For Logout,wait_until_visible,"mobile.drivers.after_upload_doc.logout_btn"
+79.Click Logout,tap,,"mobile.drivers.after_upload_doc.logout_btn"
+80.Click Confirm Logout,tap,,"mobile.drivers.after_upload_doc.logout_confirm_btn"
+81.Reload Driver App Completely,reload_app,driver,
+82.Load Admin App,switch_to,web,
+83.Wait For Dashboard,wait_until_visible,,"web.global.menu.dashboard"
+84.Click Dashboard Icon,click,,"web.global.menu.dashboard"
+85.Click drivers menu,click,,"admin.drivers.menu.icon"
+86.Click Pending Documents,click,,"admin.drivers.pending_docs.link"
+87.Filter by Name,type,{driverName},"admin.drivers.name_filter.input"
+98.Scroll Grid,tab,7,"admin.drivers.name_filter.input"
+89. Click Doc Icon,click,,"admin.drivers.docs.icon"
+90. Wait For Required Documents,wait_until_visible,,"admin.drivers.required_docs.header"
+91. FilterDocumet List,type,Driving Licence,"admin.drivers.docs_filter.input"
+92. Click Approve Driver,click,,"admin.drivers.docs.approval"
+93. Wait For Updated Successfully,wait_until_visible,,"web.global.toast.updated"
+94. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+95. Click drivers menu,click,,"admin.drivers.menu.icon"
+96. Click UnApproved Drivers,click,,"admin.drivers.unapproved_docs.link"
+97.Wait For load,wait,3000,
+98.Filter Approved Driver,type,{driverName},"admin.drivers.name_filter.input"
+99.Scroll Grid,tab,10,"admin.drivers.name_filter.input"
+100.Click Eye Icon,click,,"admin.drivers.unapproved_driver.eye_icon"
+101.Wait For Data,wait,3000,
+102.Click Close Button,click,,"admin.drivers.unapproved_driver.eye_icon.close_btn"
+103.Click ThumbsUp For Approve,click,,"admin.drivers.unapproved_driver.thumbs_up"
+104.Wait For Toast,wait,3000,
+105. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+106.Click drivers menu,click,,"admin.drivers.menu.icon"
+107.Click Approved Drivers,click,,"admin.drivers.approved_docs.link"
+108.Wait For Approved Drivers List,wait_until_visible,,"admin.drivers.approved_page.header"
+109. Filter Approved Driver,type,{driverName},"admin.drivers.name_filter.input"
+110.Load Driver App,switch_to,driver,
+111.Wait For Notification,wait_until_visible,,"mobile.driver.permission_allow.btn"
+112.Click Allow Notification,tap,,"mobile.driver.permission_allow.btn"
+113.Click Agree,tap,,"mobile.driver.agree.btn"
+114.Click Get Started,tap,,"mobile.driver.get_started.btn"
+115.Click Next,tap,,"mobile.driver.next.btn"
+116.Click Mobile Number,tap,,"mobile.driver.mobile_number_field.btn"
+117.Click Close,tap,,"mobile.driver.cancel.btn"
+118.Enter Mobile Number,type,{driverNumber},"mobile.driver.edit_text.input"
+119.Wait for Continue,wait_until_visible,,"mobile.driver.continue.btn"
+120.Click Continue,tap,,"mobile.driver.continue.btn"
+121.Enter OTP,type,123456,"mobile.driver.edit_text.input"
+122.Click Allow Location,tap,,"mobile.driver.location_allow.btn"
+123.Wait For Driver App,wait_until_visible,,"mobile.driver.app_header.label"
+124.Wait For Pageload,wait,3000,
+125. Click Select All Agree,tap,,"mobile.driver.independent_contractor.checkbox_Select_All"
+126. Wait for Agree,wait_until_visible,,"mobile.driver.agree_continue.btn"
+127. Click Agree,tap,,"mobile.driver.agree_continue.btn"
+128. Wait For OTP,wait_until_visible,,"mobile.driver.edit_text.input"
+129. Enter OTP,type,123456,"mobile.driver.edit_text.input"
+130.Force Driver Location To Perambur,set_location,13.121030;80.232578,
+131.Wait For Driver App,wait_until_visible,,"mobile.driver.app_header.label"
+132.Load Super Admin,switch_to,web,
+133.Click Dashboard Icon,click,,"web.global.menu.dashboard"
+134.Click Settings Menu,click,,"web.global.menu.settings"
+135.Click Site Settings Menu,click,,"admin.setting.site_setting.sidebar_menu"
+136.Click Wallet Status Dropdown,click,,"admin.setting.site_setting.wallet_dropdown"
+137.Wait For On,wait,2000,
+138.Select Wallet ON Option,click,,"admin.setting.site_setting.walletdropdown_option_on"
+139.Click Auto Settle Dropdown,click,,"admin.setting.site_setting.Auto_Settle_dropdown"
+140.Wait For Off,wait,2000,
+141.Select Auto Settle Off Option,click,,"admin.setting.site_setting.Auto_Settle_option_off"
+142.Click Submit Button,click,,"web.global.action.submit"
+143.Verify Settings Updated Successfully,verify,,"web.global.toast.updated"
+144.Load Driver App,switch_to,driver,
+145.Wait For Driver App,wait_until_visible,,"mobile.driver.app_header.label"
+146.Click Hamburger,tap_coordinate,75:209,COORDINATE_MODE
+147.wait for Wallet,wait_until_visible,"mobile.driver.wallet.btn"
+148.Click Wallet,tap,,"mobile.driver.wallet.btn"
+149.Wait For Topup,wait_until_visible,,"mobile.driver.top_up.btn"
+150.Click Topup,tap,,"mobile.driver.top_up.btn"
+151.Wait For Topup Sum,wait_until_visible,,"mobile.driver.top_up.btn"
+152.Click Hundered,tap,,"mobile.driver.top_up_amount.hundred"
+153.Click Proceed,tap,,"mobile.driver.top_up.proceed"
+154.Wait For Contact No,wait_until_visible,,"mobile.driver.top_up.contact_no_box"
+155.Enter Driver Mobile,type,{driverNumber},"mobile.driver.top_up.contact_no_box"
+156.Wait For Payment Options,wait_until_visible,,"mobile.driver.top_up.payment_option"
+157.Wait For Net Banking,wait_until_visible,,"mobile.driver.top_up.net_banking"
+158.Click Net Banking,tap,,"mobile.driver.top_up.net_banking"
+159.Wait For Bob,wait_until_visible,,"mobile.driver.top_up.bob_bank"
+160.Click Bob,tap,,"mobile.driver.top_up.bob_bank"
+161.Wait For Success,wait_until_visible,,"mobile.driver.top_up.succes_popup"
+162.Click Success,tap,,"mobile.driver.top_up.succes_popup"
+163.Wait For Wallet  Back,wait_until_visible,,"mobile.driver.wallet.btn"
+164.Click Back,tap,,"mobile.driver.back.btn"
+165.Drag Page Layout Upward,swipe,up,
+166.Click Back,tap,,"mobile.driver.back.btn"
+167.Wait for Load,wait,5000,
+168. Click Online Toggle,tap_coordinate,986:1936,
+169.Load Super Admin,switch_to,web,
+170.Click Dashboard,Click,,"web.global.menu.dashboard"
+171.Click Transport Service,Click,,"admin.transport.menu.card"
+172.Click Search Box,click,,"admin.transport.search.input_box"
+173.Enter Services,type,Auto Ride,"admin.transport.search.input_box"
+174.Click Home Icon,Click,,"admin.transport.home.icon"
+175.Click AerialView Button,click,,"admin.transport_service.areial_view.tab"
+176.Click All Button,click,,"admin.transport_service.areial_view.all.button"
+177.Wait For Load,wait,2000,
+178.Click AerialView Button,click,,"admin.transport_service.areial_view.tab"
+179.Click available button,click,,"admin.transport_service.areial_view.available.button"
+180.Search Driver,type,{driverName},"admin.transport.aerial_view.driver_search_field"
+181.Wait For Driver,wait,2000,
+182.Click Back Button,click,,"admin.transport_service.areial_view.back.button"
+183.Load User App,switch_to,user,
+184.Wait For Permission,wait_until_visible,,"mobile.customer.get_started.btn"
+185.Click Get Started,tap,,"mobile.customer.get_started.btn"
+186.Wait For Permission,wait_until_visible,,"mobile.customer.permission_allow.btn"
+187.Click Allow Permission,tap,,"mobile.customer.permission_allow.btn"
+188.Force Customer Location To Perambur,set_location,13.121030;80.232578,
+189.Click Next,tap,,"mobile.customer.next.btn"
+190.Click Mobile Number,tap,,"mobile.customer.mobile_number_field.btn"
+191.Click Close,tap,,"mobile.customer.cancel.btn"
+192.Enter Mobile Number,type,{randomPhone}&gt;&gt;customerPhone,"mobile.customer.edit_text.input"
+193.Click Continue,tap,,"mobile.customer.continue.btn"
+194.Wait For Otp,wait_until_visible,,"mobile.customer.otp_input"
+195.Enter OTP,type,123456,"mobile.customer.otp_input"
+196.Wait For Landing Page,wait_until_visible,,"mobile.customer.ride_complete.+91"
+197.Enter Customer Name,type,customer{randomAlpha}&gt;&gt;customerName,"mobile.customer.registration.name_input_field"
+198.Enter Customer Eamil,type,{customerName}@gmail.com,"mobile.customer.registration.email_input_field"
+199.Click Gender Male,tap,,"mobile.customer.register_customer.gender.male"
+200.Click Check Box,tap,,"mobile.customer.register_customer.checkbox"
+201.Click SignUp,tap,,"mobile.customer.register_customer.sign_up"
+202.Click Allow Location,tap,,"mobile.customer.location_allow.btn"
+203. Wait For Auto Ride,wait_until_visible,,"mobile.customer.auto_ride.btn"
+204.Click Auto Ride,tap,,"mobile.customer.auto_ride.btn"
+205.Enter Destination,type,Parsn Manare,"mobile.customer.destination.input"
+206.Wait for Location,wait_until_visible,,"mobile.customer.set_location_map.btn"
+207.Select Destination,tap,,"mobile.customer.destination_suggestion_first"
+208.Wait For Entrance,wait_until_visible,,"mobile.customer.destination_entrance_location"
+209.Click Entrance,tap,,"mobile.customer.destination_entrance_location"
+210.Click Confirm,tap,,"mobile.customer.confirm.btn"
+211.Wait For Ride,wait,5000,
+212.Wait for Ride,wait_until_visible,,"mobile.customer.ride_now.btn"
+213.Ride Now,tap,,"mobile.customer.ride_now.btn"
+214.Load Driver App,switch_to,driver,
+215.Wait for Accept,wait_until_visible,,"mobie.driver.auto_ride_accept.button"
+216.Click  Accept Ride,tap,,"mobie.driver.auto_ride_accept.button"
+217.Load User App,switch_to,user,
+218.Wait for OTP Layout to Load,wait_until_visible,,"mobile.customer.otp_display_element"
+219.Extract OTP from Screen,store_text,ride_otp,"mobile.customer.otp_display_element"
+220.Switch to web,switch_to,web,
+221.Click AerialView Button,click,,"admin.transport_service.areial_view.tab"
+222.Click Enroute to pickup,click,,"admin.transport_service.areial_view.enroute_to_pickup.button"
+223.Search Driver,type,{driverName},"admin.transport.aerial_view.driver_search_field"
+224.Wait For Driver,wait,2000,
+225.Click Eye Button,click,,"admin.transport_service.areial_view.eye.button"
+226.Wait For Aerial View,wait,5000,
+227.Click Back Button,click,,"admin.transport_service.areial_view.back.button"
+228.Load Driver App,switch_to,driver,
+229.Wait for On My Way,wait_until_visible,,"mobile.driver.on_my_way.btn"
+230.Wait for Arrived,wait_until_visible,,"mobile.driver.arrived.btn"
+231.Wait for Arrived,wait_until_visible,,"mobile.driver.arrived.btn"
+232.Ride Arrived,tap,,"mobile.driver.arrived.btn"
+233.Wait for Yes,wait_until_visible,,"mobile.driver.yes.btn"
+234.Yes Arrived,tap,,"mobile.driver.yes.btn"
+235.Switch to web,switch_to,web,
+236.Click AerialView Button,click,,"admin.transport_service.areial_view.tab"
+237.Click Reached Pickup,click,,"admin.transport_service.areial_view.reached_pickup.button"
+238.Search Driver,type,{driverName},"admin.transport.aerial_view.driver_search_field"
+239.Wait For Driver,wait,2000,
+240.Click Eye Button,click,,"admin.transport_service.areial_view.eye.button"
+241.Wait For Aerial View,wait,5000,
+242.Click Back Button,click,,"admin.transport_service.areial_view.back.button"
+243.Load Driver App,switch_to,driver,
+244.Wait for Start Ride,wait_until_visible,,"mobile.driver.start_ride.btn"
+245.Start Ride,tap,,"mobile.driver.start_ride.btn"
+246.wait for Otp,wait_until_visible,,"mobile.driver.otp_view.input"
+247.Enter  Extracted OTP,type,{ride_otp},"mobile.driver.otp_view.input"
+248.Wait for Start Button,wait_until_visible,,"mobile.driver.start.btn"
+249.Start Ride Button,tap,,"mobile.driver.start.btn"
+250.Swtich To Web,switch_to,web,
+251.Click AerialView Button,click,,"admin.transport_service.areial_view.tab"
+252.Click Ongoing Button,click,,"admin.transport_service.areial_view.ongoing.button"
+253.Search Driver,type,{driverName},"admin.transport.aerial_view.driver_search_field"
+254.Wait For Driver,wait,2000,
+255.Click Eye Button,click,,"admin.transport_service.areial_view.eye.button"
+256.Wait For Aerial View,wait,5000,
+257.Click the closed Button,click,,"admin.transport.aerial_view.eye_icon_close"
+258.Load Driver App,switch_to,driver,
+259.Wait for Complete Ride,wait_until_visible,,"mobile.driver.complete_ride.btn"
+260.Complete Ride,tap,,"mobile.driver.complete_ride.btn"
+261.Wait for Collect Payment,wait_until_visible,,"mobile.driver.collect_payment.btn" 
+262.Collect Payment,tap,,"mobile.driver.collect_payment.btn"
+263.Load User App,switch_to,user,
+264.Wait for Proceed Payment,wait_until_visible,,"mobile.customer.proceed_to_pay.btn"
+265.Proceed Payment,tap,,"mobile.customer.proceed_to_pay.btn"
+266.Wait for Proceed Pay Confirm,wait_until_visible,,"mobile.customer.proceed_to_pay.btn"
+267.Pay Cash,tap,,"mobile.customer.proceed_to_pay.btn"
+268.Wait for Review,wait_until_visible,,"mobile.customer.give_review.btn"
+269.Give Review,tap,,"mobile.customer.give_review.btn"
+270.Give Rating,tap_coordinate,348:1619,
+271.Submit Rating,tap,,"mobile.customer.submit_rating.btn"
+272.Wait for Done,wait_until_visible,,"mobile.customer.done.btn"
+273.Trip Finished,tap,,"mobile.customer.done.btn"
+274.Load Driver App,switch_to,driver,
+275.Wait  For Proceed,wait_until_visible,,"mobile.driver.payment.proceed_btn"
+276.Click For Proceed,tap,,"mobile.driver.payment.proceed_btn"
+277.Wait for Yes,wait_until_visible,,"mobile.driver.yes.btn"
+278.Confirm Payment,tap,,"mobile.driver.yes.btn"
+279.Wait For Give Review Button,wait_until_visible,,"mobile.driver.give_review.btn"
+280.Click Give Review Button,tap,,"mobile.driver.give_review.btn"
+281.Wait For Rating,wait,2000,
+282.Give Rating,tap_coordinate,348:1545,
+283.Submit Rating,tap,,"mobile.driver.submit_rating.btn"
+284.Wait for Complete Button,wait_until_visible,,"mobile.driver.complete.btn"
+285.Click Complete Button,tap,,"mobile.driver.complete.btn"
+286.Wait For  ride complete submit button,wait_until_visible,,"mobile.driver.ride_complete_submit.btn"
+287.Click Ride Complete Submit Button,tap,,"mobile.driver.ride_complete_submit.btn"
+288.Switch to Web,switch_to,web,
+289.Click Review Menu,click,,"admin.transport.reviews.top_menu_btn"
+290.Wait For Review,wait,1000,
+291.Click Today Button,Click,,"web.global.dashboard.today_statistics"
+292.Wait For Today Statistics,wait,2000,
+293.Click Search Button,click,,"admin.transport.reviews.search_btn"
+294.Wait For Load,wait,2000,
+295.Filter Customer Name List,type,{customerName},"admin.transport.reviews.customer_filter_name"
+296.Wait For Loading,wait,1000,
+297.Filter Driver Name List,type,{driverName},"admin.transport.reviews.driver_filter_name"
+298.Wait For Loading,wait,1000,
+299.Click Today Button,Click,,"web.global.dashboard.today_statistics"
+300.Click Earning Report,click,,"admin.transport.earning_reports.top_menu_btn"
+301.Click Today Button,Click,,"web.global.dashboard.today_statistics"
+302.Wait For Today Statistics,wait,2000,
+303.Click Search Button,click,,"admin.report_issue.customer_report_issues.search_btn"
+304.Wait For Load,wait,2000,
+305.Scroll Grid,tab,6,"admin.transport.reviews.payment_status_filter_name"
+306.Wait For Load,wait,2000,
+307.Filter Customer Name List,type,{customerName},"admin.transport.reviews.customer_filter_name"
+308.Wait For Loading,wait,1000,
+309.Filter Driver Name List,type,{driverName},"admin.transport.reviews.driver_filter_name"
+310.Wait For Loading,wait,1000,
+311.Scroll Grid,tab,23,"admin.transport.reviews.driver_filter_name"
+312.Enter Unsettled,type,unsettled,"admin.transport.earning_reports.payment_status_filter"
+313.Wait For Loading,wait,1000,
+314.Click Unsettled Ride,click,,"admin.transport.reviews.unsettled_ride"
+315.Wait For Loading,wait,1000,
+316.Click Settle Transaction Button,click,"admin.transport.earning_reports.mark_as_settle_btn"
+317.Wait For Loading,wait,4000,
+</t>
   </si>
 </sst>
 </file>
@@ -1517,4 +2343,111 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96677455-12DD-44D7-B364-A1FEA415895A}">
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.33203125" customWidth="1"/>
+    <col min="2" max="2" width="21.5546875" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" customWidth="1"/>
+    <col min="4" max="4" width="28.77734375" customWidth="1"/>
+    <col min="5" max="5" width="29.109375" customWidth="1"/>
+    <col min="6" max="6" width="45.77734375" customWidth="1"/>
+    <col min="7" max="7" width="71.44140625" customWidth="1"/>
+    <col min="8" max="8" width="40.44140625" customWidth="1"/>
+    <col min="9" max="9" width="39.6640625" customWidth="1"/>
+    <col min="10" max="10" width="51.109375" customWidth="1"/>
+    <col min="11" max="11" width="67" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" s="1" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/EPIC_0005_Ride_Safety_Calls.xlsx
+++ b/EPIC_0005_Ride_Safety_Calls.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Framework_For_WE1_Automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{344E7EDC-4E79-4F21-8C02-658F12A79A98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D588010-118B-45A9-9005-81CA1A9EDA39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UserDriverWebIntialilzer" sheetId="43" r:id="rId1"/>
     <sheet name="CustomerAppEmergencyNumber" sheetId="48" r:id="rId2"/>
     <sheet name="PanicCallCheck" sheetId="49" r:id="rId3"/>
     <sheet name="RideAerialViewEarningReports" sheetId="50" r:id="rId4"/>
+    <sheet name="DataCleanUpSheet" sheetId="51" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="56">
   <si>
     <t>Requirement Title</t>
   </si>
@@ -1707,12 +1708,158 @@
 317.Wait For Loading,wait,4000,
 </t>
   </si>
+  <si>
+    <t>Pre-production</t>
+  </si>
+  <si>
+    <t>QA</t>
+  </si>
+  <si>
+    <t>SA_TS_29</t>
+  </si>
+  <si>
+    <t>Clean The Test Data Created During Test Run</t>
+  </si>
+  <si>
+    <t>TC_SA_03_test_data_cleanup</t>
+  </si>
+  <si>
+    <t>This test phase ensures the long-term stability and performance of the QA environment by executing a systematic Automated Data Cleanup strategy. Leveraging localized SQL Hooks with built-in safety firewalls, the workflow identifies and removes dynamically generated test artifacts—including unique City Areas, Provider profiles, and administrative accounts—created during the regression suite. By targeting specific records using variable-driven WHERE clauses, the script maintains database referential integrity, prevents record duplication in subsequent runs, and ensures the test environment remains in a pristine, 'ready-state' for continuous integration</t>
+  </si>
+  <si>
+    <t>No Manual Test Cases Since this is a data cleanup sheet after test execution</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CRITICAL SYSTEM WARNING: DATABASE INTEGRITY PROTOCOL</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-----------------------------------------</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">This sheet contains SQL Hooks that execute directly against the we1 Production/Staging database. DO NOT modify the SQL syntax, remove variable placeholders (e.g., {areaName}), or edit the WHERE clauses.
+Unauthorized changes may result in irreversible data loss or database corruption. If modifications are required, please contact the Automation Lead or the Database Administrator.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PASSWORD TO EDIT SHEET</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> :eit6190
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Data Dependency:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The SuperAdminLogin test suite must be always executed before this test.This ensures the browser is already logged in as a Super Admin. Without this step, the automation will encounter a "Redirect to Login" or "Access Denied" error. The framework is configured to automatically handle this login for you if it hasn't been done yet.
+RunSheet: SuperAdminLogin
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <t>TC_RG_05_test_data_cleanup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.Remove  Subscrption Plan,sql delete,,"DELETE FROM we1.panic_call WHERE name = '{policeName}';"
+</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1732,6 +1879,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1763,7 +1918,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1776,6 +1931,16 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2450,4 +2615,92 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FCA0D8B-8968-4717-A6E5-49959BF0DAC0}">
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="26.77734375" customWidth="1"/>
+    <col min="5" max="6" width="34.109375" customWidth="1"/>
+    <col min="7" max="7" width="69.33203125" customWidth="1"/>
+    <col min="8" max="8" width="31.77734375" customWidth="1"/>
+    <col min="9" max="9" width="13.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="8"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>